--- a/make_table/jd_self/b_total.xlsx
+++ b/make_table/jd_self/b_total.xlsx
@@ -458,7 +458,7 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -658,7 +658,7 @@
         <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -706,7 +706,7 @@
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
